--- a/artfynd/A 3110-2026 artfynd.xlsx
+++ b/artfynd/A 3110-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133981727</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58044</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norra Sonarp,Nässjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>487813</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6383409</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3110-2026 artfynd.xlsx
+++ b/artfynd/A 3110-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>133981727</v>
       </c>
       <c r="B4" t="n">
-        <v>58044</v>
+        <v>58051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3110-2026 artfynd.xlsx
+++ b/artfynd/A 3110-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>133981727</v>
       </c>
       <c r="B4" t="n">
-        <v>58051</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3110-2026 artfynd.xlsx
+++ b/artfynd/A 3110-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>78462986</v>
       </c>
       <c r="B2" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487812.6146456346</v>
+        <v>487813</v>
       </c>
       <c r="R2" t="n">
-        <v>6383408.704189719</v>
+        <v>6383409</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -798,15 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88980347</v>
+        <v>95887686</v>
       </c>
       <c r="B3" t="n">
-        <v>56315</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102110</v>
+        <v>100100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,21 +826,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Sonarp,Nässjö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487812.6146456346</v>
+        <v>487813</v>
       </c>
       <c r="R3" t="n">
-        <v>6383408.704189719</v>
+        <v>6383409</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,22 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133981727</v>
+        <v>88980347</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>57903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>102110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,14 +937,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -998,22 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,6 +1017,238 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99478980</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norra Sonarp,Nässjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>487813</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6383409</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-03-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-03-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133981727</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norra Sonarp,Nässjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>487813</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6383409</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3110-2026 artfynd.xlsx
+++ b/artfynd/A 3110-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78462986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95887686</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88980347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99478980</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,8 +1274,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133981727</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>